--- a/research/traditional_assets/database/data/switzerland/switzerland_reinsurance.xlsx
+++ b/research/traditional_assets/database/data/switzerland/switzerland_reinsurance.xlsx
@@ -588,124 +588,118 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0392</v>
-      </c>
-      <c r="E2">
-        <v>-0.211</v>
+        <v>0.0199</v>
       </c>
       <c r="F2">
-        <v>0.13</v>
+        <v>0.4970000000000001</v>
       </c>
       <c r="G2">
-        <v>-0.009069525968934754</v>
+        <v>0.05373674007275262</v>
       </c>
       <c r="H2">
-        <v>-0.009069525968934754</v>
+        <v>0.05373674007275262</v>
       </c>
       <c r="I2">
-        <v>0.04749506236461621</v>
+        <v>0.0044130514952692</v>
       </c>
       <c r="J2">
-        <v>0.03643920461703334</v>
+        <v>0.0044130514952692</v>
       </c>
       <c r="K2">
-        <v>1303</v>
+        <v>-106</v>
       </c>
       <c r="L2">
-        <v>0.02761119705028501</v>
+        <v>-0.002308915463198937</v>
       </c>
       <c r="M2">
-        <v>1887</v>
+        <v>0</v>
       </c>
       <c r="N2">
-        <v>0.06613580445952293</v>
+        <v>0</v>
       </c>
       <c r="O2">
-        <v>1.448196469685342</v>
+        <v>-0</v>
       </c>
       <c r="P2">
-        <v>1855</v>
+        <v>0</v>
       </c>
       <c r="Q2">
-        <v>0.06501426458527558</v>
+        <v>0</v>
       </c>
       <c r="R2">
-        <v>1.423637759017652</v>
+        <v>-0</v>
       </c>
       <c r="S2">
-        <v>32</v>
-      </c>
-      <c r="T2">
-        <v>0.01695813460519343</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>7296</v>
+        <v>4631</v>
       </c>
       <c r="V2">
-        <v>0.2557110913283939</v>
+        <v>0.1713636565474164</v>
       </c>
       <c r="W2">
-        <v>0.04664733469373143</v>
+        <v>-0.004452846040747742</v>
       </c>
       <c r="X2">
-        <v>0.09543037052422555</v>
+        <v>0.1263868182784983</v>
       </c>
       <c r="Y2">
-        <v>-0.04878303583049412</v>
+        <v>-0.1308396643192461</v>
       </c>
       <c r="Z2">
-        <v>1.741602932574548</v>
+        <v>1.792549649575304</v>
       </c>
       <c r="AA2">
-        <v>0.06346262562170928</v>
+        <v>0.007910613911402577</v>
       </c>
       <c r="AB2">
-        <v>0.07237263339914035</v>
+        <v>0.1013825636042874</v>
       </c>
       <c r="AC2">
-        <v>-0.008910007777431075</v>
+        <v>-0.09347194969288478</v>
       </c>
       <c r="AD2">
-        <v>12675</v>
+        <v>11239</v>
       </c>
       <c r="AE2">
-        <v>523.3025597569833</v>
+        <v>427.0060945184315</v>
       </c>
       <c r="AF2">
-        <v>13198.30255975698</v>
+        <v>11666.00609451843</v>
       </c>
       <c r="AG2">
-        <v>5902.302559756983</v>
+        <v>7035.006094518432</v>
       </c>
       <c r="AH2">
-        <v>0.3162747091496768</v>
+        <v>0.3015219345596697</v>
       </c>
       <c r="AI2">
-        <v>0.3555165120883386</v>
+        <v>0.4926105519928361</v>
       </c>
       <c r="AJ2">
-        <v>0.1714066451087609</v>
+        <v>0.2065510500974548</v>
       </c>
       <c r="AK2">
-        <v>0.1978759115753408</v>
+        <v>0.3692721560013895</v>
       </c>
       <c r="AL2">
-        <v>572</v>
+        <v>590</v>
       </c>
       <c r="AM2">
-        <v>572</v>
+        <v>590</v>
       </c>
       <c r="AN2">
-        <v>5.252797347699959</v>
+        <v>32.29597701149425</v>
       </c>
       <c r="AO2">
-        <v>3.944055944055944</v>
+        <v>0.3423728813559322</v>
       </c>
       <c r="AP2">
-        <v>2.446043331851215</v>
+        <v>20.21553475436331</v>
       </c>
       <c r="AQ2">
-        <v>3.944055944055944</v>
+        <v>0.3423728813559322</v>
       </c>
     </row>
     <row r="3">
@@ -725,124 +719,118 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0392</v>
-      </c>
-      <c r="E3">
-        <v>-0.211</v>
+        <v>0.0199</v>
       </c>
       <c r="F3">
-        <v>0.13</v>
+        <v>0.4970000000000001</v>
       </c>
       <c r="G3">
-        <v>-0.009069525968934754</v>
+        <v>0.05373674007275262</v>
       </c>
       <c r="H3">
-        <v>-0.009069525968934754</v>
+        <v>0.05373674007275262</v>
       </c>
       <c r="I3">
-        <v>0.04749506236461621</v>
+        <v>0.0044130514952692</v>
       </c>
       <c r="J3">
-        <v>0.03643920461703334</v>
+        <v>0.0044130514952692</v>
       </c>
       <c r="K3">
-        <v>1303</v>
+        <v>-106</v>
       </c>
       <c r="L3">
-        <v>0.02761119705028501</v>
+        <v>-0.002308915463198937</v>
       </c>
       <c r="M3">
-        <v>1887</v>
+        <v>-0</v>
       </c>
       <c r="N3">
-        <v>0.06613580445952293</v>
+        <v>-0</v>
       </c>
       <c r="O3">
-        <v>1.448196469685342</v>
+        <v>0</v>
       </c>
       <c r="P3">
-        <v>1855</v>
+        <v>-0</v>
       </c>
       <c r="Q3">
-        <v>0.06501426458527558</v>
+        <v>-0</v>
       </c>
       <c r="R3">
-        <v>1.423637759017652</v>
+        <v>0</v>
       </c>
       <c r="S3">
-        <v>32</v>
-      </c>
-      <c r="T3">
-        <v>0.01695813460519343</v>
+        <v>0</v>
       </c>
       <c r="U3">
-        <v>7296</v>
+        <v>4631</v>
       </c>
       <c r="V3">
-        <v>0.2557110913283939</v>
+        <v>0.1713636565474164</v>
       </c>
       <c r="W3">
-        <v>0.04664733469373143</v>
+        <v>-0.004452846040747742</v>
       </c>
       <c r="X3">
-        <v>0.09543037052422555</v>
+        <v>0.1263868182784983</v>
       </c>
       <c r="Y3">
-        <v>-0.04878303583049412</v>
+        <v>-0.1308396643192461</v>
       </c>
       <c r="Z3">
-        <v>1.741602932574548</v>
+        <v>1.792549649575304</v>
       </c>
       <c r="AA3">
-        <v>0.06346262562170928</v>
+        <v>0.007910613911402577</v>
       </c>
       <c r="AB3">
-        <v>0.07237263339914035</v>
+        <v>0.1013825636042874</v>
       </c>
       <c r="AC3">
-        <v>-0.008910007777431075</v>
+        <v>-0.09347194969288478</v>
       </c>
       <c r="AD3">
-        <v>12675</v>
+        <v>11239</v>
       </c>
       <c r="AE3">
-        <v>523.3025597569833</v>
+        <v>427.0060945184315</v>
       </c>
       <c r="AF3">
-        <v>13198.30255975698</v>
+        <v>11666.00609451843</v>
       </c>
       <c r="AG3">
-        <v>5902.302559756983</v>
+        <v>7035.006094518432</v>
       </c>
       <c r="AH3">
-        <v>0.3162747091496768</v>
+        <v>0.3015219345596697</v>
       </c>
       <c r="AI3">
-        <v>0.3555165120883386</v>
+        <v>0.4926105519928361</v>
       </c>
       <c r="AJ3">
-        <v>0.1714066451087609</v>
+        <v>0.2065510500974548</v>
       </c>
       <c r="AK3">
-        <v>0.1978759115753408</v>
+        <v>0.3692721560013895</v>
       </c>
       <c r="AL3">
-        <v>572</v>
+        <v>590</v>
       </c>
       <c r="AM3">
-        <v>572</v>
+        <v>590</v>
       </c>
       <c r="AN3">
-        <v>5.252797347699959</v>
+        <v>32.29597701149425</v>
       </c>
       <c r="AO3">
-        <v>3.944055944055944</v>
+        <v>0.3423728813559322</v>
       </c>
       <c r="AP3">
-        <v>2.446043331851215</v>
+        <v>20.21553475436331</v>
       </c>
       <c r="AQ3">
-        <v>3.944055944055944</v>
+        <v>0.3423728813559322</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/switzerland/switzerland_reinsurance.xlsx
+++ b/research/traditional_assets/database/data/switzerland/switzerland_reinsurance.xlsx
@@ -588,28 +588,31 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0199</v>
+        <v>0.0455</v>
+      </c>
+      <c r="E2">
+        <v>0.585</v>
       </c>
       <c r="F2">
-        <v>0.4970000000000001</v>
+        <v>0.544</v>
       </c>
       <c r="G2">
-        <v>0.05373674007275262</v>
+        <v>0.02667701609608628</v>
       </c>
       <c r="H2">
-        <v>0.05373674007275262</v>
+        <v>0.02667701609608628</v>
       </c>
       <c r="I2">
-        <v>0.0044130514952692</v>
+        <v>0.09883896461088205</v>
       </c>
       <c r="J2">
-        <v>0.0044130514952692</v>
+        <v>0.07558411245012829</v>
       </c>
       <c r="K2">
-        <v>-106</v>
+        <v>3223</v>
       </c>
       <c r="L2">
-        <v>-0.002308915463198937</v>
+        <v>0.06583462701201079</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -618,7 +621,7 @@
         <v>0</v>
       </c>
       <c r="O2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -627,79 +630,79 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
       <c r="U2">
-        <v>4631</v>
+        <v>5288</v>
       </c>
       <c r="V2">
-        <v>0.1713636565474164</v>
+        <v>0.1621548689391245</v>
       </c>
       <c r="W2">
-        <v>-0.004452846040747742</v>
+        <v>0.2706129303106633</v>
       </c>
       <c r="X2">
-        <v>0.1263868182784983</v>
+        <v>0.1027632426517971</v>
       </c>
       <c r="Y2">
-        <v>-0.1308396643192461</v>
+        <v>0.1678496876588662</v>
       </c>
       <c r="Z2">
-        <v>1.792549649575304</v>
+        <v>3.229884521967519</v>
       </c>
       <c r="AA2">
-        <v>0.007910613911402577</v>
+        <v>0.2441279549093218</v>
       </c>
       <c r="AB2">
-        <v>0.1013825636042874</v>
+        <v>0.08708458974058858</v>
       </c>
       <c r="AC2">
-        <v>-0.09347194969288478</v>
+        <v>0.1570433651687333</v>
       </c>
       <c r="AD2">
-        <v>11239</v>
+        <v>11003</v>
       </c>
       <c r="AE2">
-        <v>427.0060945184315</v>
+        <v>411.1982425482901</v>
       </c>
       <c r="AF2">
-        <v>11666.00609451843</v>
+        <v>11414.19824254829</v>
       </c>
       <c r="AG2">
-        <v>7035.006094518432</v>
+        <v>6126.198242548289</v>
       </c>
       <c r="AH2">
-        <v>0.3015219345596697</v>
+        <v>0.259266296381517</v>
       </c>
       <c r="AI2">
-        <v>0.4926105519928361</v>
+        <v>0.4692720968980783</v>
       </c>
       <c r="AJ2">
-        <v>0.2065510500974548</v>
+        <v>0.1581485019616038</v>
       </c>
       <c r="AK2">
-        <v>0.3692721560013895</v>
+        <v>0.3218352740269733</v>
       </c>
       <c r="AL2">
-        <v>590</v>
+        <v>604</v>
       </c>
       <c r="AM2">
-        <v>590</v>
+        <v>604</v>
       </c>
       <c r="AN2">
-        <v>32.29597701149425</v>
+        <v>2.195331205107741</v>
       </c>
       <c r="AO2">
-        <v>0.3423728813559322</v>
+        <v>8.02980132450331</v>
       </c>
       <c r="AP2">
-        <v>20.21553475436331</v>
+        <v>1.22230611383645</v>
       </c>
       <c r="AQ2">
-        <v>0.3423728813559322</v>
+        <v>8.02980132450331</v>
       </c>
     </row>
     <row r="3">
@@ -719,28 +722,31 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0199</v>
+        <v>0.0455</v>
+      </c>
+      <c r="E3">
+        <v>0.585</v>
       </c>
       <c r="F3">
-        <v>0.4970000000000001</v>
+        <v>0.544</v>
       </c>
       <c r="G3">
-        <v>0.05373674007275262</v>
+        <v>0.02667701609608628</v>
       </c>
       <c r="H3">
-        <v>0.05373674007275262</v>
+        <v>0.02667701609608628</v>
       </c>
       <c r="I3">
-        <v>0.0044130514952692</v>
+        <v>0.09883896461088205</v>
       </c>
       <c r="J3">
-        <v>0.0044130514952692</v>
+        <v>0.07558411245012829</v>
       </c>
       <c r="K3">
-        <v>-106</v>
+        <v>3223</v>
       </c>
       <c r="L3">
-        <v>-0.002308915463198937</v>
+        <v>0.06583462701201079</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -749,7 +755,7 @@
         <v>-0</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -758,79 +764,79 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
       <c r="U3">
-        <v>4631</v>
+        <v>5288</v>
       </c>
       <c r="V3">
-        <v>0.1713636565474164</v>
+        <v>0.1621548689391245</v>
       </c>
       <c r="W3">
-        <v>-0.004452846040747742</v>
+        <v>0.2706129303106633</v>
       </c>
       <c r="X3">
-        <v>0.1263868182784983</v>
+        <v>0.1027632426517971</v>
       </c>
       <c r="Y3">
-        <v>-0.1308396643192461</v>
+        <v>0.1678496876588662</v>
       </c>
       <c r="Z3">
-        <v>1.792549649575304</v>
+        <v>3.229884521967519</v>
       </c>
       <c r="AA3">
-        <v>0.007910613911402577</v>
+        <v>0.2441279549093218</v>
       </c>
       <c r="AB3">
-        <v>0.1013825636042874</v>
+        <v>0.08708458974058858</v>
       </c>
       <c r="AC3">
-        <v>-0.09347194969288478</v>
+        <v>0.1570433651687333</v>
       </c>
       <c r="AD3">
-        <v>11239</v>
+        <v>11003</v>
       </c>
       <c r="AE3">
-        <v>427.0060945184315</v>
+        <v>411.1982425482901</v>
       </c>
       <c r="AF3">
-        <v>11666.00609451843</v>
+        <v>11414.19824254829</v>
       </c>
       <c r="AG3">
-        <v>7035.006094518432</v>
+        <v>6126.198242548289</v>
       </c>
       <c r="AH3">
-        <v>0.3015219345596697</v>
+        <v>0.259266296381517</v>
       </c>
       <c r="AI3">
-        <v>0.4926105519928361</v>
+        <v>0.4692720968980783</v>
       </c>
       <c r="AJ3">
-        <v>0.2065510500974548</v>
+        <v>0.1581485019616038</v>
       </c>
       <c r="AK3">
-        <v>0.3692721560013895</v>
+        <v>0.3218352740269733</v>
       </c>
       <c r="AL3">
-        <v>590</v>
+        <v>604</v>
       </c>
       <c r="AM3">
-        <v>590</v>
+        <v>604</v>
       </c>
       <c r="AN3">
-        <v>32.29597701149425</v>
+        <v>2.195331205107741</v>
       </c>
       <c r="AO3">
-        <v>0.3423728813559322</v>
+        <v>8.02980132450331</v>
       </c>
       <c r="AP3">
-        <v>20.21553475436331</v>
+        <v>1.22230611383645</v>
       </c>
       <c r="AQ3">
-        <v>0.3423728813559322</v>
+        <v>8.02980132450331</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/switzerland/switzerland_reinsurance.xlsx
+++ b/research/traditional_assets/database/data/switzerland/switzerland_reinsurance.xlsx
@@ -588,121 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0455</v>
+        <v>-8.999999999999999E-05</v>
       </c>
       <c r="E2">
-        <v>0.585</v>
+        <v>0.395</v>
       </c>
       <c r="F2">
-        <v>0.544</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="G2">
-        <v>0.02667701609608628</v>
+        <v>0.1109972081661141</v>
       </c>
       <c r="H2">
-        <v>0.02667701609608628</v>
+        <v>0.1109972081661141</v>
       </c>
       <c r="I2">
-        <v>0.09883896461088205</v>
+        <v>0.1024104168744282</v>
       </c>
       <c r="J2">
-        <v>0.07558411245012829</v>
+        <v>0.0731574170178397</v>
       </c>
       <c r="K2">
-        <v>3223</v>
+        <v>2938</v>
       </c>
       <c r="L2">
-        <v>0.06583462701201079</v>
+        <v>0.06408131216192636</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>1974.72</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>0.04696570422870189</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>0.6721307011572497</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>1974.72</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>0.04696570422870189</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.6721307011572497</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
+      <c r="T2">
+        <v>0</v>
+      </c>
       <c r="U2">
-        <v>5288</v>
+        <v>4515</v>
       </c>
       <c r="V2">
-        <v>0.1621548689391245</v>
+        <v>0.1073823907149313</v>
       </c>
       <c r="W2">
-        <v>0.2706129303106633</v>
+        <v>0.2313750196881399</v>
       </c>
       <c r="X2">
-        <v>0.1027632426517971</v>
+        <v>0.09965061128505762</v>
       </c>
       <c r="Y2">
-        <v>0.1678496876588662</v>
+        <v>0.1317244084030822</v>
       </c>
       <c r="Z2">
-        <v>3.229884521967519</v>
+        <v>3.065026309606159</v>
       </c>
       <c r="AA2">
-        <v>0.2441279549093218</v>
+        <v>0.2242294079025081</v>
       </c>
       <c r="AB2">
-        <v>0.08708458974058858</v>
+        <v>0.09119979414191685</v>
       </c>
       <c r="AC2">
-        <v>0.1570433651687333</v>
+        <v>0.1330296137605912</v>
       </c>
       <c r="AD2">
-        <v>11003</v>
+        <v>7508</v>
       </c>
       <c r="AE2">
-        <v>411.1982425482901</v>
+        <v>418.4360357060834</v>
       </c>
       <c r="AF2">
-        <v>11414.19824254829</v>
+        <v>7926.436035706083</v>
       </c>
       <c r="AG2">
-        <v>6126.198242548289</v>
+        <v>3411.436035706083</v>
       </c>
       <c r="AH2">
-        <v>0.259266296381517</v>
+        <v>0.1586161625189239</v>
       </c>
       <c r="AI2">
-        <v>0.4692720968980783</v>
+        <v>0.2566565464588164</v>
       </c>
       <c r="AJ2">
-        <v>0.1581485019616038</v>
+        <v>0.07504682034918238</v>
       </c>
       <c r="AK2">
-        <v>0.3218352740269733</v>
+        <v>0.1293757442074525</v>
       </c>
       <c r="AL2">
-        <v>604</v>
+        <v>448</v>
       </c>
       <c r="AM2">
-        <v>604</v>
+        <v>448</v>
       </c>
       <c r="AN2">
-        <v>2.195331205107741</v>
+        <v>1.549382970820091</v>
       </c>
       <c r="AO2">
-        <v>8.02980132450331</v>
+        <v>10.50446428571429</v>
       </c>
       <c r="AP2">
-        <v>1.22230611383645</v>
+        <v>0.7039985215456855</v>
       </c>
       <c r="AQ2">
-        <v>8.02980132450331</v>
+        <v>10.50446428571429</v>
       </c>
     </row>
     <row r="3">
@@ -722,121 +725,124 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0455</v>
+        <v>-8.999999999999999E-05</v>
       </c>
       <c r="E3">
-        <v>0.585</v>
+        <v>0.395</v>
       </c>
       <c r="F3">
-        <v>0.544</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="G3">
-        <v>0.02667701609608628</v>
+        <v>0.1109972081661141</v>
       </c>
       <c r="H3">
-        <v>0.02667701609608628</v>
+        <v>0.1109972081661141</v>
       </c>
       <c r="I3">
-        <v>0.09883896461088205</v>
+        <v>0.1024104168744282</v>
       </c>
       <c r="J3">
-        <v>0.07558411245012829</v>
+        <v>0.0731574170178397</v>
       </c>
       <c r="K3">
-        <v>3223</v>
+        <v>2938</v>
       </c>
       <c r="L3">
-        <v>0.06583462701201079</v>
+        <v>0.06408131216192636</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>1974.72</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.04696570422870189</v>
       </c>
       <c r="O3">
-        <v>-0</v>
+        <v>0.6721307011572497</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>1974.72</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.04696570422870189</v>
       </c>
       <c r="R3">
-        <v>-0</v>
+        <v>0.6721307011572497</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
       <c r="U3">
-        <v>5288</v>
+        <v>4515</v>
       </c>
       <c r="V3">
-        <v>0.1621548689391245</v>
+        <v>0.1073823907149313</v>
       </c>
       <c r="W3">
-        <v>0.2706129303106633</v>
+        <v>0.2313750196881399</v>
       </c>
       <c r="X3">
-        <v>0.1027632426517971</v>
+        <v>0.09965061128505762</v>
       </c>
       <c r="Y3">
-        <v>0.1678496876588662</v>
+        <v>0.1317244084030822</v>
       </c>
       <c r="Z3">
-        <v>3.229884521967519</v>
+        <v>3.065026309606159</v>
       </c>
       <c r="AA3">
-        <v>0.2441279549093218</v>
+        <v>0.2242294079025081</v>
       </c>
       <c r="AB3">
-        <v>0.08708458974058858</v>
+        <v>0.09119979414191685</v>
       </c>
       <c r="AC3">
-        <v>0.1570433651687333</v>
+        <v>0.1330296137605912</v>
       </c>
       <c r="AD3">
-        <v>11003</v>
+        <v>7508</v>
       </c>
       <c r="AE3">
-        <v>411.1982425482901</v>
+        <v>418.4360357060834</v>
       </c>
       <c r="AF3">
-        <v>11414.19824254829</v>
+        <v>7926.436035706083</v>
       </c>
       <c r="AG3">
-        <v>6126.198242548289</v>
+        <v>3411.436035706083</v>
       </c>
       <c r="AH3">
-        <v>0.259266296381517</v>
+        <v>0.1586161625189239</v>
       </c>
       <c r="AI3">
-        <v>0.4692720968980783</v>
+        <v>0.2566565464588164</v>
       </c>
       <c r="AJ3">
-        <v>0.1581485019616038</v>
+        <v>0.07504682034918238</v>
       </c>
       <c r="AK3">
-        <v>0.3218352740269733</v>
+        <v>0.1293757442074525</v>
       </c>
       <c r="AL3">
-        <v>604</v>
+        <v>448</v>
       </c>
       <c r="AM3">
-        <v>604</v>
+        <v>448</v>
       </c>
       <c r="AN3">
-        <v>2.195331205107741</v>
+        <v>1.549382970820091</v>
       </c>
       <c r="AO3">
-        <v>8.02980132450331</v>
+        <v>10.50446428571429</v>
       </c>
       <c r="AP3">
-        <v>1.22230611383645</v>
+        <v>0.7039985215456855</v>
       </c>
       <c r="AQ3">
-        <v>8.02980132450331</v>
+        <v>10.50446428571429</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/switzerland/switzerland_reinsurance.xlsx
+++ b/research/traditional_assets/database/data/switzerland/switzerland_reinsurance.xlsx
@@ -648,10 +648,10 @@
         <v>0.2313750196881399</v>
       </c>
       <c r="X2">
-        <v>0.09965061128505762</v>
+        <v>0.09961599012988775</v>
       </c>
       <c r="Y2">
-        <v>0.1317244084030822</v>
+        <v>0.1317590295582521</v>
       </c>
       <c r="Z2">
         <v>3.065026309606159</v>
@@ -660,10 +660,10 @@
         <v>0.2242294079025081</v>
       </c>
       <c r="AB2">
-        <v>0.09119979414191685</v>
+        <v>0.09117066446152201</v>
       </c>
       <c r="AC2">
-        <v>0.1330296137605912</v>
+        <v>0.1330587434409861</v>
       </c>
       <c r="AD2">
         <v>7508</v>
@@ -785,10 +785,10 @@
         <v>0.2313750196881399</v>
       </c>
       <c r="X3">
-        <v>0.09965061128505762</v>
+        <v>0.09961599012988775</v>
       </c>
       <c r="Y3">
-        <v>0.1317244084030822</v>
+        <v>0.1317590295582521</v>
       </c>
       <c r="Z3">
         <v>3.065026309606159</v>
@@ -797,10 +797,10 @@
         <v>0.2242294079025081</v>
       </c>
       <c r="AB3">
-        <v>0.09119979414191685</v>
+        <v>0.09117066446152201</v>
       </c>
       <c r="AC3">
-        <v>0.1330296137605912</v>
+        <v>0.1330587434409861</v>
       </c>
       <c r="AD3">
         <v>7508</v>
